--- a/assessment_forms/027_tech_product_development_assessment_form--assessment_forms.xlsx
+++ b/assessment_forms/027_tech_product_development_assessment_form--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'high',_'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'High', 'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Medium', 'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'low',_'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Low', 'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'john',_'value':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'John', 'value': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'jane',_'value':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Jane', 'value': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'None', 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'john',_'value':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'John', 'value': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'jane',_'value':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Jane', 'value': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress',_'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress', 'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'on_hold',_'value':_'on_hold'}</t>
+          <t>on_hold</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'On Hold', 'value': 'On Hold'}</t>
+          <t>On Hold</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'closed',_'value':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Closed', 'value': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'cancelled',_'value':_'cancelled'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Cancelled', 'value': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'1-5',_'value':_'1-5'}</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': '1-5', 'value': '1-5'}</t>
+          <t>1-5</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'6-10',_'value':_'6-10'}</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': '6-10', 'value': '6-10'}</t>
+          <t>6-10</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'11-20',_'value':_'11-20'}</t>
+          <t>11-20</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': '11-20', 'value': '11-20'}</t>
+          <t>11-20</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'21+',_'value':_'21+'}</t>
+          <t>21+</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': '21+', 'value': '21+'}</t>
+          <t>21+</t>
         </is>
       </c>
     </row>
